--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N70_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N70_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>121.1132873653176</v>
+        <v>19.68090919686412</v>
       </c>
       <c r="D2" t="n">
-        <v>109.4936551112553</v>
+        <v>17.79271895557898</v>
       </c>
       <c r="E2" t="n">
-        <v>28.31845322063567</v>
+        <v>4.601748648353295</v>
       </c>
       <c r="F2" t="n">
-        <v>23.20730579444846</v>
+        <v>3.771187191597875</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>101.0386216607256</v>
+        <v>16.41877601986791</v>
       </c>
       <c r="D3" t="n">
-        <v>90.74370450855844</v>
+        <v>14.74585198264075</v>
       </c>
       <c r="E3" t="n">
-        <v>28.31845322063567</v>
+        <v>4.601748648353295</v>
       </c>
       <c r="F3" t="n">
-        <v>23.20730579444846</v>
+        <v>3.771187191597875</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>69.68830316635393</v>
+        <v>11.32434926453251</v>
       </c>
       <c r="D4" t="n">
-        <v>63.30553278418707</v>
+        <v>10.2871490774304</v>
       </c>
       <c r="E4" t="n">
-        <v>28.31845322063567</v>
+        <v>4.601748648353295</v>
       </c>
       <c r="F4" t="n">
-        <v>23.20730579444846</v>
+        <v>3.771187191597875</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>59.58966045976332</v>
+        <v>9.683319824711539</v>
       </c>
       <c r="D5" t="n">
-        <v>55.80495524169478</v>
+        <v>9.068305226775403</v>
       </c>
       <c r="E5" t="n">
-        <v>28.31845322063567</v>
+        <v>4.601748648353295</v>
       </c>
       <c r="F5" t="n">
-        <v>23.20730579444846</v>
+        <v>3.771187191597875</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>58.5044592030298</v>
+        <v>9.506974620492342</v>
       </c>
       <c r="D6" t="n">
-        <v>56.43411064069134</v>
+        <v>9.170542979112343</v>
       </c>
       <c r="E6" t="n">
-        <v>28.31845322063567</v>
+        <v>4.601748648353295</v>
       </c>
       <c r="F6" t="n">
-        <v>23.20730579444846</v>
+        <v>3.771187191597875</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>43.71925336814967</v>
+        <v>7.104378672324322</v>
       </c>
       <c r="D7" t="n">
-        <v>44.82557512822007</v>
+        <v>7.284155958335761</v>
       </c>
       <c r="E7" t="n">
-        <v>28.31845322063567</v>
+        <v>4.601748648353295</v>
       </c>
       <c r="F7" t="n">
-        <v>23.20730579444846</v>
+        <v>3.771187191597875</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>68.44739170119675</v>
+        <v>11.12270115144447</v>
       </c>
       <c r="D8" t="n">
-        <v>64.44924439774724</v>
+        <v>10.47300221463393</v>
       </c>
       <c r="E8" t="n">
-        <v>28.31845322063567</v>
+        <v>4.601748648353295</v>
       </c>
       <c r="F8" t="n">
-        <v>23.20730579444846</v>
+        <v>3.771187191597875</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>32.3566784993945</v>
+        <v>5.257960256151607</v>
       </c>
       <c r="D9" t="n">
-        <v>41.33449795157701</v>
+        <v>6.716855917131264</v>
       </c>
       <c r="E9" t="n">
-        <v>28.31845322063567</v>
+        <v>4.601748648353295</v>
       </c>
       <c r="F9" t="n">
-        <v>23.20730579444846</v>
+        <v>3.771187191597875</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>21.34574707109083</v>
+        <v>3.468683899052259</v>
       </c>
       <c r="D10" t="n">
-        <v>31.63095200326542</v>
+        <v>5.140029700530632</v>
       </c>
       <c r="E10" t="n">
-        <v>28.31845322063567</v>
+        <v>4.601748648353295</v>
       </c>
       <c r="F10" t="n">
-        <v>23.20730579444846</v>
+        <v>3.771187191597875</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>46.44895601596308</v>
+        <v>7.547955352594001</v>
       </c>
       <c r="D11" t="n">
-        <v>30.46099509573222</v>
+        <v>4.949911703056485</v>
       </c>
       <c r="E11" t="n">
-        <v>28.31845322063567</v>
+        <v>4.601748648353295</v>
       </c>
       <c r="F11" t="n">
-        <v>23.20730579444846</v>
+        <v>3.771187191597875</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>87.4222532969695</v>
+        <v>14.20611616075754</v>
       </c>
       <c r="D12" t="n">
-        <v>74.60768980072059</v>
+        <v>12.1237495926171</v>
       </c>
       <c r="E12" t="n">
-        <v>28.31845322063567</v>
+        <v>4.601748648353295</v>
       </c>
       <c r="F12" t="n">
-        <v>23.20730579444846</v>
+        <v>3.771187191597875</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
